--- a/temp_output/water_body_statistics.xlsx
+++ b/temp_output/water_body_statistics.xlsx
@@ -655,98 +655,160 @@
           <t>Type</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n">
-        <v>1990</v>
-      </c>
-      <c r="C1" s="1" t="n">
-        <v>1991</v>
-      </c>
-      <c r="D1" s="1" t="n">
-        <v>1992</v>
-      </c>
-      <c r="E1" s="1" t="n">
-        <v>1993</v>
-      </c>
-      <c r="F1" s="1" t="n">
-        <v>1994</v>
-      </c>
-      <c r="G1" s="1" t="n">
-        <v>1995</v>
-      </c>
-      <c r="H1" s="1" t="n">
-        <v>1996</v>
-      </c>
-      <c r="I1" s="1" t="n">
-        <v>1997</v>
-      </c>
-      <c r="J1" s="1" t="n">
-        <v>1998</v>
-      </c>
-      <c r="K1" s="1" t="n">
-        <v>1999</v>
-      </c>
-      <c r="L1" s="1" t="n">
-        <v>2000</v>
-      </c>
-      <c r="M1" s="1" t="n">
-        <v>2001</v>
-      </c>
-      <c r="N1" s="1" t="n">
-        <v>2002</v>
-      </c>
-      <c r="O1" s="1" t="n">
-        <v>2003</v>
-      </c>
-      <c r="P1" s="1" t="n">
-        <v>2004</v>
-      </c>
-      <c r="Q1" s="1" t="n">
-        <v>2005</v>
-      </c>
-      <c r="R1" s="1" t="n">
-        <v>2006</v>
-      </c>
-      <c r="S1" s="1" t="n">
-        <v>2007</v>
-      </c>
-      <c r="T1" s="1" t="n">
-        <v>2008</v>
-      </c>
-      <c r="U1" s="1" t="n">
-        <v>2009</v>
-      </c>
-      <c r="V1" s="1" t="n">
-        <v>2010</v>
-      </c>
-      <c r="W1" s="1" t="n">
-        <v>2011</v>
-      </c>
-      <c r="X1" s="1" t="n">
-        <v>2012</v>
-      </c>
-      <c r="Y1" s="1" t="n">
-        <v>2013</v>
-      </c>
-      <c r="Z1" s="1" t="n">
-        <v>2014</v>
-      </c>
-      <c r="AA1" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="AB1" s="1" t="n">
-        <v>2016</v>
-      </c>
-      <c r="AC1" s="1" t="n">
-        <v>2017</v>
-      </c>
-      <c r="AD1" s="1" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AE1" s="1" t="n">
-        <v>2019</v>
-      </c>
-      <c r="AF1" s="1" t="n">
-        <v>2020</v>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
       </c>
     </row>
     <row r="2">
@@ -1081,8 +1143,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>1990</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
       </c>
       <c r="B2" t="n">
         <v>570</v>
@@ -1092,8 +1156,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1991</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
       </c>
       <c r="B3" t="n">
         <v>855</v>
@@ -1103,8 +1169,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>1992</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
       </c>
       <c r="B4" t="n">
         <v>353</v>
@@ -1114,8 +1182,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>1993</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
       </c>
       <c r="B5" t="n">
         <v>417</v>
@@ -1125,8 +1195,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>1994</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
       </c>
       <c r="B6" t="n">
         <v>400</v>
@@ -1136,8 +1208,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>1995</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
       </c>
       <c r="B7" t="n">
         <v>512</v>
@@ -1147,8 +1221,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>1996</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
       </c>
       <c r="B8" t="n">
         <v>145</v>
@@ -1158,8 +1234,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>1997</v>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
       </c>
       <c r="B9" t="n">
         <v>41</v>
@@ -1169,8 +1247,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>1998</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
       </c>
       <c r="B10" t="n">
         <v>1391</v>
@@ -1180,8 +1260,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>1999</v>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
       </c>
       <c r="B11" t="n">
         <v>1363</v>
@@ -1191,8 +1273,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>2000</v>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
       <c r="B12" t="n">
         <v>1331</v>
@@ -1202,8 +1286,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>2001</v>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
       </c>
       <c r="B13" t="n">
         <v>1320</v>
@@ -1213,8 +1299,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>2002</v>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
       </c>
       <c r="B14" t="n">
         <v>1350</v>
@@ -1224,8 +1312,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>2003</v>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
       </c>
       <c r="B15" t="n">
         <v>1405</v>
@@ -1235,8 +1325,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>2004</v>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
       </c>
       <c r="B16" t="n">
         <v>1469</v>
@@ -1246,8 +1338,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>2005</v>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
       </c>
       <c r="B17" t="n">
         <v>1478</v>
@@ -1257,8 +1351,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>2006</v>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
       </c>
       <c r="B18" t="n">
         <v>1477</v>
@@ -1268,8 +1364,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>2007</v>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
       </c>
       <c r="B19" t="n">
         <v>1587</v>
@@ -1279,8 +1377,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>2008</v>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
       </c>
       <c r="B20" t="n">
         <v>1580</v>
@@ -1290,8 +1390,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>2009</v>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
       </c>
       <c r="B21" t="n">
         <v>1613</v>
@@ -1301,8 +1403,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>2010</v>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
       </c>
       <c r="B22" t="n">
         <v>1604</v>
@@ -1312,8 +1416,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>2011</v>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
       </c>
       <c r="B23" t="n">
         <v>1692</v>
@@ -1323,8 +1429,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>2012</v>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
       </c>
       <c r="B24" t="n">
         <v>1740</v>
@@ -1334,8 +1442,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>2013</v>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
       </c>
       <c r="B25" t="n">
         <v>1941</v>
@@ -1345,8 +1455,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>2014</v>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
       </c>
       <c r="B26" t="n">
         <v>1966</v>
@@ -1356,8 +1468,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>2015</v>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
       </c>
       <c r="B27" t="n">
         <v>2335</v>
@@ -1367,8 +1481,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>2016</v>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
       </c>
       <c r="B28" t="n">
         <v>2528</v>
@@ -1378,8 +1494,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>2017</v>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
       </c>
       <c r="B29" t="n">
         <v>2560</v>
@@ -1389,8 +1507,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>2018</v>
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
       </c>
       <c r="B30" t="n">
         <v>2589</v>
@@ -1400,8 +1520,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>2019</v>
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
       </c>
       <c r="B31" t="n">
         <v>2754</v>
@@ -1411,8 +1533,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>2020</v>
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
       </c>
       <c r="B32" t="n">
         <v>2907</v>
@@ -1473,8 +1597,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>1990</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
       </c>
       <c r="B2" t="n">
         <v>476</v>
@@ -1496,8 +1622,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1991</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
       </c>
       <c r="B3" t="n">
         <v>704</v>
@@ -1519,8 +1647,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>1992</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
       </c>
       <c r="B4" t="n">
         <v>264</v>
@@ -1542,8 +1672,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>1993</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
       </c>
       <c r="B5" t="n">
         <v>289</v>
@@ -1565,8 +1697,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>1994</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
       </c>
       <c r="B6" t="n">
         <v>248</v>
@@ -1588,8 +1722,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>1995</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
       </c>
       <c r="B7" t="n">
         <v>295</v>
@@ -1611,8 +1747,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>1996</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
       </c>
       <c r="B8" t="n">
         <v>124</v>
@@ -1634,8 +1772,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>1997</v>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
       </c>
       <c r="B9" t="n">
         <v>31</v>
@@ -1657,8 +1797,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>1998</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
       </c>
       <c r="B10" t="n">
         <v>1071</v>
@@ -1680,8 +1822,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>1999</v>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
       </c>
       <c r="B11" t="n">
         <v>1060</v>
@@ -1703,8 +1847,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>2000</v>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
       <c r="B12" t="n">
         <v>1030</v>
@@ -1726,8 +1872,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>2001</v>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
       </c>
       <c r="B13" t="n">
         <v>1007</v>
@@ -1749,8 +1897,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>2002</v>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
       </c>
       <c r="B14" t="n">
         <v>1053</v>
@@ -1772,8 +1922,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>2003</v>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
       </c>
       <c r="B15" t="n">
         <v>1108</v>
@@ -1795,8 +1947,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>2004</v>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
       </c>
       <c r="B16" t="n">
         <v>1133</v>
@@ -1818,8 +1972,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>2005</v>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
       </c>
       <c r="B17" t="n">
         <v>1145</v>
@@ -1841,8 +1997,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>2006</v>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
       </c>
       <c r="B18" t="n">
         <v>1150</v>
@@ -1864,8 +2022,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>2007</v>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
       </c>
       <c r="B19" t="n">
         <v>1227</v>
@@ -1887,8 +2047,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>2008</v>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
       </c>
       <c r="B20" t="n">
         <v>1237</v>
@@ -1910,8 +2072,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>2009</v>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
       </c>
       <c r="B21" t="n">
         <v>1262</v>
@@ -1933,8 +2097,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>2010</v>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
       </c>
       <c r="B22" t="n">
         <v>1271</v>
@@ -1956,8 +2122,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>2011</v>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
       </c>
       <c r="B23" t="n">
         <v>1326</v>
@@ -1979,8 +2147,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>2012</v>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
       </c>
       <c r="B24" t="n">
         <v>1366</v>
@@ -2002,8 +2172,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>2013</v>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
       </c>
       <c r="B25" t="n">
         <v>1477</v>
@@ -2025,8 +2197,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>2014</v>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
       </c>
       <c r="B26" t="n">
         <v>1498</v>
@@ -2048,8 +2222,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>2015</v>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
       </c>
       <c r="B27" t="n">
         <v>1716</v>
@@ -2071,8 +2247,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>2016</v>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
       </c>
       <c r="B28" t="n">
         <v>1815</v>
@@ -2094,8 +2272,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>2017</v>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
       </c>
       <c r="B29" t="n">
         <v>1858</v>
@@ -2117,8 +2297,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>2018</v>
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
       </c>
       <c r="B30" t="n">
         <v>1859</v>
@@ -2140,8 +2322,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>2019</v>
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
       </c>
       <c r="B31" t="n">
         <v>1946</v>
@@ -2163,8 +2347,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>2020</v>
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
       </c>
       <c r="B32" t="n">
         <v>2035</v>
